--- a/public/clickson.xlsx
+++ b/public/clickson.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RomainCABC\Documents\git\PEBC\clickson-api\api\public\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RomainCABC\Documents\git\PEBC\clickson\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0EE840C-7B2A-48D4-8255-8384BD57EB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B868936A-648D-4BB2-9DAC-3608AED2274E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Accueil" sheetId="1" r:id="rId1"/>
     <sheet name="Synthèse &amp; Profil" sheetId="2" r:id="rId2"/>
     <sheet name="FE" sheetId="12" r:id="rId3"/>
-    <sheet name="Plan daction" sheetId="3" r:id="rId4"/>
-    <sheet name="Energie" sheetId="4" r:id="rId5"/>
-    <sheet name="Restauration" sheetId="5" r:id="rId6"/>
-    <sheet name="Déplacements" sheetId="6" r:id="rId7"/>
-    <sheet name="Achats" sheetId="7" r:id="rId8"/>
-    <sheet name="Immobilisations" sheetId="8" r:id="rId9"/>
+    <sheet name="Energie" sheetId="4" r:id="rId4"/>
+    <sheet name="Restauration" sheetId="5" r:id="rId5"/>
+    <sheet name="Déplacements" sheetId="6" r:id="rId6"/>
+    <sheet name="Achats" sheetId="7" r:id="rId7"/>
+    <sheet name="Immobilisations" sheetId="8" r:id="rId8"/>
+    <sheet name="Plan daction" sheetId="3" r:id="rId9"/>
     <sheet name="Objectifs de réduction" sheetId="9" state="hidden" r:id="rId10"/>
     <sheet name="Actions" sheetId="10" state="hidden" r:id="rId11"/>
     <sheet name="Conclusion" sheetId="11" state="hidden" r:id="rId12"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="313">
   <si>
     <t xml:space="preserve">Calculateur Clicks On - Export de données </t>
   </si>
@@ -791,6 +791,255 @@
   </si>
   <si>
     <t>Plaques de cuisson/au gaz 9000W</t>
+  </si>
+  <si>
+    <t>3,19</t>
+  </si>
+  <si>
+    <t>3,25</t>
+  </si>
+  <si>
+    <t>2,32</t>
+  </si>
+  <si>
+    <t>0,027</t>
+  </si>
+  <si>
+    <t>0,074</t>
+  </si>
+  <si>
+    <t>0,132</t>
+  </si>
+  <si>
+    <t>0,0647</t>
+  </si>
+  <si>
+    <t>2,25</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>7,26</t>
+  </si>
+  <si>
+    <t>1,58</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>0,49</t>
+  </si>
+  <si>
+    <t>3,59</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>2,57</t>
+  </si>
+  <si>
+    <t>7,25</t>
+  </si>
+  <si>
+    <t>0,379</t>
+  </si>
+  <si>
+    <t>0,848</t>
+  </si>
+  <si>
+    <t>0,178</t>
+  </si>
+  <si>
+    <t>0,105</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>2,51</t>
+  </si>
+  <si>
+    <t>0,0226</t>
+  </si>
+  <si>
+    <t>0,00146</t>
+  </si>
+  <si>
+    <t>0,0331</t>
+  </si>
+  <si>
+    <t>0,0137</t>
+  </si>
+  <si>
+    <t>0,0109</t>
+  </si>
+  <si>
+    <t>0,0249</t>
+  </si>
+  <si>
+    <t>0,239</t>
+  </si>
+  <si>
+    <t>0,227</t>
+  </si>
+  <si>
+    <t>0,0763</t>
+  </si>
+  <si>
+    <t>0,103</t>
+  </si>
+  <si>
+    <t>0,0217</t>
+  </si>
+  <si>
+    <t>0,122</t>
+  </si>
+  <si>
+    <t>0,146</t>
+  </si>
+  <si>
+    <t>0,137</t>
+  </si>
+  <si>
+    <t>0,129</t>
+  </si>
+  <si>
+    <t>0,0057</t>
+  </si>
+  <si>
+    <t>0,006</t>
+  </si>
+  <si>
+    <t>0,00369</t>
+  </si>
+  <si>
+    <t>0,367</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>0,917</t>
+  </si>
+  <si>
+    <t>2,29</t>
+  </si>
+  <si>
+    <t>0,0653</t>
+  </si>
+  <si>
+    <t>1,44</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>0,215</t>
+  </si>
+  <si>
+    <t>1,29</t>
+  </si>
+  <si>
+    <t>0,472</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>1,47</t>
+  </si>
+  <si>
+    <t>0,535</t>
+  </si>
+  <si>
+    <t>0,637</t>
+  </si>
+  <si>
+    <t>0,547</t>
+  </si>
+  <si>
+    <t>4,18</t>
+  </si>
+  <si>
+    <t>1,23</t>
+  </si>
+  <si>
+    <t>1,18</t>
+  </si>
+  <si>
+    <t>1,31</t>
+  </si>
+  <si>
+    <t>5,5</t>
+  </si>
+  <si>
+    <t>0,8</t>
+  </si>
+  <si>
+    <t>4,6</t>
+  </si>
+  <si>
+    <t>4,12</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>0,92</t>
+  </si>
+  <si>
+    <t>63,2</t>
+  </si>
+  <si>
+    <t>2,78</t>
+  </si>
+  <si>
+    <t>80,7</t>
+  </si>
+  <si>
+    <t>8,98</t>
+  </si>
+  <si>
+    <t>32,8</t>
+  </si>
+  <si>
+    <t>87,9</t>
+  </si>
+  <si>
+    <t>60,1</t>
+  </si>
+  <si>
+    <t>18,6</t>
+  </si>
+  <si>
+    <t>34,4</t>
+  </si>
+  <si>
+    <t>70,1</t>
+  </si>
+  <si>
+    <t>9,9</t>
+  </si>
+  <si>
+    <t>98,4</t>
+  </si>
+  <si>
+    <t>31,9</t>
+  </si>
+  <si>
+    <t>22,5</t>
+  </si>
+  <si>
+    <t>43,4</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1436,11 +1685,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1449,6 +1693,11 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1463,6 +1712,96 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="21" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2933,7 +3272,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="22.8">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="121" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="115"/>
@@ -2959,17 +3298,17 @@
       <c r="J2" s="115"/>
     </row>
     <row r="3" spans="1:10" ht="13.2">
-      <c r="A3" s="125" t="s">
+      <c r="A3" s="122" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="115"/>
       <c r="C3" s="115"/>
       <c r="D3" s="115"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="126" t="s">
+      <c r="F3" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="127"/>
+      <c r="G3" s="124"/>
       <c r="H3" s="8" t="s">
         <v>16</v>
       </c>
@@ -3134,7 +3473,7 @@
       <c r="J13" s="115"/>
     </row>
     <row r="14" spans="1:10" ht="13.2">
-      <c r="A14" s="121" t="s">
+      <c r="A14" s="125" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="14" t="s">
@@ -3150,7 +3489,7 @@
       <c r="J14" s="115"/>
     </row>
     <row r="15" spans="1:10" ht="13.2">
-      <c r="A15" s="122"/>
+      <c r="A15" s="126"/>
       <c r="B15" s="14" t="s">
         <v>20</v>
       </c>
@@ -3164,7 +3503,7 @@
       <c r="J15" s="115"/>
     </row>
     <row r="16" spans="1:10" ht="13.2">
-      <c r="A16" s="122"/>
+      <c r="A16" s="126"/>
       <c r="B16" s="14" t="s">
         <v>21</v>
       </c>
@@ -3178,7 +3517,7 @@
       <c r="J16" s="115"/>
     </row>
     <row r="17" spans="1:10" ht="26.4">
-      <c r="A17" s="123"/>
+      <c r="A17" s="127"/>
       <c r="B17" s="16" t="s">
         <v>22</v>
       </c>
@@ -3192,7 +3531,7 @@
       <c r="J17" s="115"/>
     </row>
     <row r="18" spans="1:10" ht="13.2">
-      <c r="A18" s="121" t="s">
+      <c r="A18" s="125" t="s">
         <v>5</v>
       </c>
       <c r="B18" s="16" t="s">
@@ -3208,7 +3547,7 @@
       <c r="J18" s="115"/>
     </row>
     <row r="19" spans="1:10" ht="13.2">
-      <c r="A19" s="122"/>
+      <c r="A19" s="126"/>
       <c r="B19" s="16" t="s">
         <v>24</v>
       </c>
@@ -3222,7 +3561,7 @@
       <c r="J19" s="115"/>
     </row>
     <row r="20" spans="1:10" ht="13.2">
-      <c r="A20" s="122"/>
+      <c r="A20" s="126"/>
       <c r="B20" s="16" t="s">
         <v>25</v>
       </c>
@@ -3236,7 +3575,7 @@
       <c r="J20" s="115"/>
     </row>
     <row r="21" spans="1:10" ht="13.2">
-      <c r="A21" s="123"/>
+      <c r="A21" s="127"/>
       <c r="B21" s="16" t="s">
         <v>26</v>
       </c>
@@ -3250,7 +3589,7 @@
       <c r="J21" s="115"/>
     </row>
     <row r="22" spans="1:10" ht="13.2">
-      <c r="A22" s="121" t="s">
+      <c r="A22" s="125" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="16" t="s">
@@ -3266,7 +3605,7 @@
       <c r="J22" s="115"/>
     </row>
     <row r="23" spans="1:10" ht="13.2">
-      <c r="A23" s="122"/>
+      <c r="A23" s="126"/>
       <c r="B23" s="16" t="s">
         <v>28</v>
       </c>
@@ -3280,7 +3619,7 @@
       <c r="J23" s="115"/>
     </row>
     <row r="24" spans="1:10" ht="13.2">
-      <c r="A24" s="123"/>
+      <c r="A24" s="127"/>
       <c r="B24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3294,7 +3633,7 @@
       <c r="J24" s="115"/>
     </row>
     <row r="25" spans="1:10" ht="13.2">
-      <c r="A25" s="121" t="s">
+      <c r="A25" s="125" t="s">
         <v>7</v>
       </c>
       <c r="B25" s="16" t="s">
@@ -3310,7 +3649,7 @@
       <c r="J25" s="115"/>
     </row>
     <row r="26" spans="1:10" ht="13.2">
-      <c r="A26" s="122"/>
+      <c r="A26" s="126"/>
       <c r="B26" s="16" t="s">
         <v>31</v>
       </c>
@@ -3324,7 +3663,7 @@
       <c r="J26" s="115"/>
     </row>
     <row r="27" spans="1:10" ht="13.2">
-      <c r="A27" s="122"/>
+      <c r="A27" s="126"/>
       <c r="B27" s="16" t="s">
         <v>32</v>
       </c>
@@ -3338,7 +3677,7 @@
       <c r="J27" s="115"/>
     </row>
     <row r="28" spans="1:10" ht="13.2">
-      <c r="A28" s="123"/>
+      <c r="A28" s="127"/>
       <c r="B28" s="16" t="s">
         <v>33</v>
       </c>
@@ -3352,7 +3691,7 @@
       <c r="J28" s="115"/>
     </row>
     <row r="29" spans="1:10" ht="13.2">
-      <c r="A29" s="121" t="s">
+      <c r="A29" s="125" t="s">
         <v>10</v>
       </c>
       <c r="B29" s="16" t="s">
@@ -3368,7 +3707,7 @@
       <c r="J29" s="115"/>
     </row>
     <row r="30" spans="1:10" ht="13.2">
-      <c r="A30" s="122"/>
+      <c r="A30" s="126"/>
       <c r="B30" s="16" t="s">
         <v>35</v>
       </c>
@@ -3382,7 +3721,7 @@
       <c r="J30" s="115"/>
     </row>
     <row r="31" spans="1:10" ht="13.2">
-      <c r="A31" s="122"/>
+      <c r="A31" s="126"/>
       <c r="B31" s="16" t="s">
         <v>36</v>
       </c>
@@ -3396,7 +3735,7 @@
       <c r="J31" s="115"/>
     </row>
     <row r="32" spans="1:10" ht="13.2">
-      <c r="A32" s="123"/>
+      <c r="A32" s="127"/>
       <c r="B32" s="16" t="s">
         <v>37</v>
       </c>
@@ -4429,24 +4768,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <sheetData>
-    <row r="2" spans="1:1">
-      <c r="A2" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFCE5CD"/>
@@ -4456,8 +4777,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="55.109375" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" style="134" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="18.88671875" customWidth="1"/>
     <col min="8" max="23" width="3" customWidth="1"/>
     <col min="24" max="43" width="12.6640625" hidden="1"/>
@@ -4528,8 +4849,8 @@
         <v>45</v>
       </c>
       <c r="B4" s="22"/>
-      <c r="C4" s="22">
-        <v>3.19</v>
+      <c r="C4" s="103" t="s">
+        <v>230</v>
       </c>
       <c r="D4" s="22"/>
       <c r="E4" s="22" t="s">
@@ -4547,8 +4868,8 @@
         <v>48</v>
       </c>
       <c r="B5" s="22"/>
-      <c r="C5" s="22">
-        <v>3.25</v>
+      <c r="C5" s="103" t="s">
+        <v>231</v>
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="22" t="s">
@@ -4566,8 +4887,8 @@
         <v>49</v>
       </c>
       <c r="B6" s="22"/>
-      <c r="C6" s="22">
-        <v>2.3199999999999998</v>
+      <c r="C6" s="103" t="s">
+        <v>232</v>
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="22" t="s">
@@ -4601,8 +4922,8 @@
         <v>52</v>
       </c>
       <c r="B7" s="22"/>
-      <c r="C7" s="22">
-        <v>2.7E-2</v>
+      <c r="C7" s="103" t="s">
+        <v>233</v>
       </c>
       <c r="D7" s="22"/>
       <c r="E7" s="22" t="s">
@@ -4634,8 +4955,8 @@
         <v>54</v>
       </c>
       <c r="B8" s="22"/>
-      <c r="C8" s="22">
-        <v>7.3999999999999996E-2</v>
+      <c r="C8" s="103" t="s">
+        <v>234</v>
       </c>
       <c r="D8" s="22"/>
       <c r="E8" s="22" t="s">
@@ -4667,8 +4988,8 @@
         <v>55</v>
       </c>
       <c r="B9" s="22"/>
-      <c r="C9" s="22">
-        <v>0.13200000000000001</v>
+      <c r="C9" s="103" t="s">
+        <v>235</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22" t="s">
@@ -4697,7 +5018,7 @@
     </row>
     <row r="10" spans="1:23" ht="13.2">
       <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
+      <c r="C10" s="40"/>
       <c r="D10" s="24"/>
       <c r="E10" s="24"/>
       <c r="F10" s="24"/>
@@ -4718,7 +5039,7 @@
       <c r="V10" s="115"/>
     </row>
     <row r="11" spans="1:23" ht="13.2">
-      <c r="C11" s="24"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="24"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
@@ -4780,8 +5101,8 @@
         <v>57</v>
       </c>
       <c r="B13" s="22"/>
-      <c r="C13" s="22">
-        <v>6.4699999999999994E-2</v>
+      <c r="C13" s="103" t="s">
+        <v>236</v>
       </c>
       <c r="D13" s="22"/>
       <c r="E13" s="22" t="s">
@@ -4813,8 +5134,8 @@
         <v>58</v>
       </c>
       <c r="B14" s="22"/>
-      <c r="C14" s="22">
-        <v>6.4699999999999994E-2</v>
+      <c r="C14" s="103" t="s">
+        <v>236</v>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="22" t="s">
@@ -4846,8 +5167,8 @@
         <v>59</v>
       </c>
       <c r="B15" s="22"/>
-      <c r="C15" s="22">
-        <v>6.4699999999999994E-2</v>
+      <c r="C15" s="103" t="s">
+        <v>236</v>
       </c>
       <c r="D15" s="22"/>
       <c r="E15" s="22" t="s">
@@ -4879,8 +5200,8 @@
         <v>60</v>
       </c>
       <c r="B16" s="22"/>
-      <c r="C16" s="22">
-        <v>6.4699999999999994E-2</v>
+      <c r="C16" s="103" t="s">
+        <v>236</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22" t="s">
@@ -4912,8 +5233,8 @@
         <v>61</v>
       </c>
       <c r="B17" s="22"/>
-      <c r="C17" s="22">
-        <v>6.4699999999999994E-2</v>
+      <c r="C17" s="103" t="s">
+        <v>236</v>
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22" t="s">
@@ -4945,8 +5266,8 @@
         <v>62</v>
       </c>
       <c r="B18" s="22"/>
-      <c r="C18" s="22">
-        <v>6.4699999999999994E-2</v>
+      <c r="C18" s="103" t="s">
+        <v>236</v>
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="22" t="s">
@@ -4978,8 +5299,8 @@
         <v>63</v>
       </c>
       <c r="B19" s="22"/>
-      <c r="C19" s="22">
-        <v>6.4699999999999994E-2</v>
+      <c r="C19" s="103" t="s">
+        <v>236</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22" t="s">
@@ -5011,8 +5332,8 @@
         <v>64</v>
       </c>
       <c r="B20" s="22"/>
-      <c r="C20" s="22">
-        <v>6.4699999999999994E-2</v>
+      <c r="C20" s="103" t="s">
+        <v>236</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22" t="s">
@@ -5044,8 +5365,8 @@
         <v>65</v>
       </c>
       <c r="B21" s="22"/>
-      <c r="C21" s="22">
-        <v>6.4699999999999994E-2</v>
+      <c r="C21" s="103" t="s">
+        <v>236</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="22" t="s">
@@ -5077,8 +5398,8 @@
         <v>66</v>
       </c>
       <c r="B22" s="22"/>
-      <c r="C22" s="22">
-        <v>6.4699999999999994E-2</v>
+      <c r="C22" s="103" t="s">
+        <v>236</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="22" t="s">
@@ -5096,8 +5417,8 @@
         <v>67</v>
       </c>
       <c r="B23" s="22"/>
-      <c r="C23" s="22">
-        <v>6.4699999999999994E-2</v>
+      <c r="C23" s="103" t="s">
+        <v>236</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22" t="s">
@@ -5115,8 +5436,8 @@
         <v>68</v>
       </c>
       <c r="B24" s="22"/>
-      <c r="C24" s="22">
-        <v>6.4699999999999994E-2</v>
+      <c r="C24" s="103" t="s">
+        <v>236</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22" t="s">
@@ -5157,7 +5478,7 @@
         <v>69</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="25">
+      <c r="C28" s="26">
         <v>1300</v>
       </c>
       <c r="D28" s="25"/>
@@ -5176,7 +5497,7 @@
         <v>71</v>
       </c>
       <c r="B29" s="25"/>
-      <c r="C29" s="25">
+      <c r="C29" s="26">
         <v>1760</v>
       </c>
       <c r="D29" s="25"/>
@@ -5195,7 +5516,7 @@
         <v>72</v>
       </c>
       <c r="B30" s="25"/>
-      <c r="C30" s="25">
+      <c r="C30" s="26">
         <v>675</v>
       </c>
       <c r="D30" s="25"/>
@@ -5214,7 +5535,7 @@
         <v>73</v>
       </c>
       <c r="B31" s="25"/>
-      <c r="C31" s="25">
+      <c r="C31" s="26">
         <v>3943</v>
       </c>
       <c r="D31" s="25"/>
@@ -5233,7 +5554,7 @@
         <v>74</v>
       </c>
       <c r="B32" s="25"/>
-      <c r="C32" s="25">
+      <c r="C32" s="26">
         <v>1624</v>
       </c>
       <c r="D32" s="25"/>
@@ -5252,7 +5573,7 @@
         <v>75</v>
       </c>
       <c r="B33" s="25"/>
-      <c r="C33" s="25">
+      <c r="C33" s="26">
         <v>2088</v>
       </c>
       <c r="D33" s="25"/>
@@ -5271,7 +5592,7 @@
         <v>76</v>
       </c>
       <c r="B34" s="25"/>
-      <c r="C34" s="25">
+      <c r="C34" s="26">
         <v>2140</v>
       </c>
       <c r="D34" s="25"/>
@@ -5290,7 +5611,7 @@
         <v>77</v>
       </c>
       <c r="B35" s="25"/>
-      <c r="C35" s="25">
+      <c r="C35" s="26">
         <v>631</v>
       </c>
       <c r="D35" s="25"/>
@@ -5309,7 +5630,7 @@
         <v>78</v>
       </c>
       <c r="B36" s="25"/>
-      <c r="C36" s="25">
+      <c r="C36" s="26">
         <v>1</v>
       </c>
       <c r="D36" s="25"/>
@@ -5326,7 +5647,7 @@
     <row r="37" spans="1:7" ht="13.2">
       <c r="A37" s="27"/>
       <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
+      <c r="C37" s="28"/>
       <c r="D37" s="27"/>
       <c r="E37" s="27"/>
       <c r="F37" s="27"/>
@@ -5358,7 +5679,7 @@
         <v>79</v>
       </c>
       <c r="B40" s="25"/>
-      <c r="C40" s="25">
+      <c r="C40" s="26">
         <v>1</v>
       </c>
       <c r="D40" s="25"/>
@@ -5377,7 +5698,7 @@
         <v>80</v>
       </c>
       <c r="B41" s="25"/>
-      <c r="C41" s="25">
+      <c r="C41" s="26">
         <v>30</v>
       </c>
       <c r="D41" s="25"/>
@@ -5396,7 +5717,7 @@
         <v>81</v>
       </c>
       <c r="B42" s="25"/>
-      <c r="C42" s="25">
+      <c r="C42" s="26">
         <v>28</v>
       </c>
       <c r="D42" s="25"/>
@@ -5415,7 +5736,7 @@
         <v>82</v>
       </c>
       <c r="B43" s="25"/>
-      <c r="C43" s="25">
+      <c r="C43" s="26">
         <v>265</v>
       </c>
       <c r="D43" s="25"/>
@@ -5434,7 +5755,7 @@
         <v>83</v>
       </c>
       <c r="B44" s="25"/>
-      <c r="C44" s="25">
+      <c r="C44" s="26">
         <v>23500</v>
       </c>
       <c r="D44" s="25"/>
@@ -5453,7 +5774,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="25"/>
-      <c r="C45" s="25">
+      <c r="C45" s="26">
         <v>16100</v>
       </c>
       <c r="D45" s="25"/>
@@ -5470,7 +5791,7 @@
     <row r="46" spans="1:7" ht="13.2">
       <c r="A46" s="27"/>
       <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
+      <c r="C46" s="28"/>
       <c r="D46" s="27"/>
       <c r="E46" s="27"/>
       <c r="F46" s="28"/>
@@ -5479,7 +5800,7 @@
     <row r="47" spans="1:7" ht="13.2">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
+      <c r="C47" s="135"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
@@ -6452,7 +6773,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFCE5CD"/>
@@ -6463,7 +6784,7 @@
   <cols>
     <col min="1" max="1" width="49.109375" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="134" customWidth="1"/>
     <col min="4" max="7" width="18.88671875" customWidth="1"/>
     <col min="8" max="19" width="3" customWidth="1"/>
     <col min="20" max="39" width="12.6640625" hidden="1"/>
@@ -6513,8 +6834,8 @@
         <v>86</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="31">
-        <v>2.25</v>
+      <c r="C4" s="23" t="s">
+        <v>237</v>
       </c>
       <c r="D4" s="31"/>
       <c r="E4" s="31" t="s">
@@ -6533,8 +6854,8 @@
         <v>88</v>
       </c>
       <c r="B5" s="31"/>
-      <c r="C5" s="31">
-        <v>0.45</v>
+      <c r="C5" s="23" t="s">
+        <v>238</v>
       </c>
       <c r="D5" s="31"/>
       <c r="E5" s="31" t="s">
@@ -6565,8 +6886,8 @@
         <v>89</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="31">
-        <v>7.26</v>
+      <c r="C6" s="23" t="s">
+        <v>239</v>
       </c>
       <c r="D6" s="31"/>
       <c r="E6" s="31" t="s">
@@ -6595,8 +6916,8 @@
         <v>90</v>
       </c>
       <c r="B7" s="31"/>
-      <c r="C7" s="31">
-        <v>1.58</v>
+      <c r="C7" s="23" t="s">
+        <v>240</v>
       </c>
       <c r="D7" s="31"/>
       <c r="E7" s="31" t="s">
@@ -6671,8 +6992,8 @@
         <v>91</v>
       </c>
       <c r="B10" s="31"/>
-      <c r="C10" s="31">
-        <v>0.18</v>
+      <c r="C10" s="23" t="s">
+        <v>241</v>
       </c>
       <c r="D10" s="31"/>
       <c r="E10" s="31" t="s">
@@ -6700,8 +7021,8 @@
         <v>92</v>
       </c>
       <c r="B11" s="31"/>
-      <c r="C11" s="31">
-        <v>0.49</v>
+      <c r="C11" s="23" t="s">
+        <v>242</v>
       </c>
       <c r="D11" s="31"/>
       <c r="E11" s="31" t="s">
@@ -6729,8 +7050,8 @@
         <v>93</v>
       </c>
       <c r="B12" s="31"/>
-      <c r="C12" s="31">
-        <v>3.59</v>
+      <c r="C12" s="23" t="s">
+        <v>243</v>
       </c>
       <c r="D12" s="31"/>
       <c r="E12" s="31" t="s">
@@ -6758,8 +7079,8 @@
         <v>94</v>
       </c>
       <c r="B13" s="31"/>
-      <c r="C13" s="31">
-        <v>0.1</v>
+      <c r="C13" s="23" t="s">
+        <v>244</v>
       </c>
       <c r="D13" s="31"/>
       <c r="E13" s="31" t="s">
@@ -6787,8 +7108,8 @@
         <v>95</v>
       </c>
       <c r="B14" s="31"/>
-      <c r="C14" s="31">
-        <v>0.6</v>
+      <c r="C14" s="23" t="s">
+        <v>245</v>
       </c>
       <c r="D14" s="31"/>
       <c r="E14" s="31" t="s">
@@ -6816,8 +7137,8 @@
         <v>96</v>
       </c>
       <c r="B15" s="31"/>
-      <c r="C15" s="31">
-        <v>0.04</v>
+      <c r="C15" s="23" t="s">
+        <v>246</v>
       </c>
       <c r="D15" s="31"/>
       <c r="E15" s="31" t="s">
@@ -6845,8 +7166,8 @@
         <v>97</v>
       </c>
       <c r="B16" s="31"/>
-      <c r="C16" s="31">
-        <v>2.57</v>
+      <c r="C16" s="23" t="s">
+        <v>247</v>
       </c>
       <c r="D16" s="31"/>
       <c r="E16" s="31" t="s">
@@ -6874,8 +7195,8 @@
         <v>98</v>
       </c>
       <c r="B17" s="31"/>
-      <c r="C17" s="31">
-        <v>7.25</v>
+      <c r="C17" s="23" t="s">
+        <v>248</v>
       </c>
       <c r="D17" s="31"/>
       <c r="E17" s="31" t="s">
@@ -6901,7 +7222,7 @@
     <row r="18" spans="1:21" ht="13.2">
       <c r="A18" s="34"/>
       <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
+      <c r="C18" s="12"/>
       <c r="D18" s="35"/>
       <c r="E18" s="35"/>
       <c r="F18" s="36"/>
@@ -6932,15 +7253,15 @@
       <c r="T19" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="U19" s="127"/>
+      <c r="U19" s="124"/>
     </row>
     <row r="20" spans="1:21" ht="13.2">
       <c r="A20" s="37" t="s">
         <v>100</v>
       </c>
       <c r="B20" s="38"/>
-      <c r="C20" s="38">
-        <v>0.379</v>
+      <c r="C20" s="23" t="s">
+        <v>249</v>
       </c>
       <c r="D20" s="39"/>
       <c r="E20" s="39" t="s">
@@ -6964,8 +7285,8 @@
         <v>103</v>
       </c>
       <c r="B21" s="38"/>
-      <c r="C21" s="38">
-        <v>0.84799999999999998</v>
+      <c r="C21" s="23" t="s">
+        <v>250</v>
       </c>
       <c r="D21" s="39"/>
       <c r="E21" s="39" t="s">
@@ -6989,8 +7310,8 @@
         <v>105</v>
       </c>
       <c r="B22" s="38"/>
-      <c r="C22" s="38">
-        <v>0.17799999999999999</v>
+      <c r="C22" s="23" t="s">
+        <v>251</v>
       </c>
       <c r="D22" s="39"/>
       <c r="E22" s="39" t="s">
@@ -7014,8 +7335,8 @@
         <v>107</v>
       </c>
       <c r="B23" s="38"/>
-      <c r="C23" s="38">
-        <v>0.105</v>
+      <c r="C23" s="23" t="s">
+        <v>252</v>
       </c>
       <c r="D23" s="39"/>
       <c r="E23" s="39" t="s">
@@ -7039,8 +7360,8 @@
         <v>109</v>
       </c>
       <c r="B24" s="38"/>
-      <c r="C24" s="38">
-        <v>1.2</v>
+      <c r="C24" s="23" t="s">
+        <v>253</v>
       </c>
       <c r="D24" s="39"/>
       <c r="E24" s="39" t="s">
@@ -7064,8 +7385,8 @@
         <v>111</v>
       </c>
       <c r="B25" s="31"/>
-      <c r="C25" s="31">
-        <v>2.5099999999999998</v>
+      <c r="C25" s="23" t="s">
+        <v>254</v>
       </c>
       <c r="D25" s="31"/>
       <c r="E25" s="31" t="s">
@@ -7089,8 +7410,8 @@
         <v>113</v>
       </c>
       <c r="B26" s="31"/>
-      <c r="C26" s="31">
-        <v>2.2599999999999999E-2</v>
+      <c r="C26" s="23" t="s">
+        <v>255</v>
       </c>
       <c r="D26" s="31"/>
       <c r="E26" s="31" t="s">
@@ -7108,8 +7429,8 @@
         <v>114</v>
       </c>
       <c r="B27" s="31"/>
-      <c r="C27" s="31">
-        <v>1.4599999999999999E-3</v>
+      <c r="C27" s="23" t="s">
+        <v>256</v>
       </c>
       <c r="D27" s="31"/>
       <c r="E27" s="31" t="s">
@@ -7127,8 +7448,8 @@
         <v>115</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="31">
-        <v>3.3099999999999997E-2</v>
+      <c r="C28" s="23" t="s">
+        <v>257</v>
       </c>
       <c r="D28" s="31"/>
       <c r="E28" s="31" t="s">
@@ -7146,8 +7467,8 @@
         <v>116</v>
       </c>
       <c r="B29" s="31"/>
-      <c r="C29" s="31">
-        <v>1.37E-2</v>
+      <c r="C29" s="23" t="s">
+        <v>258</v>
       </c>
       <c r="D29" s="31"/>
       <c r="E29" s="31" t="s">
@@ -7163,7 +7484,7 @@
     <row r="30" spans="1:21" ht="13.2">
       <c r="A30" s="34"/>
       <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
+      <c r="C30" s="12"/>
       <c r="D30" s="35"/>
       <c r="E30" s="35"/>
       <c r="F30" s="41"/>
@@ -7197,7 +7518,7 @@
         <v>117</v>
       </c>
       <c r="B32" s="31"/>
-      <c r="C32" s="31">
+      <c r="C32" s="23">
         <v>424</v>
       </c>
       <c r="D32" s="31"/>
@@ -7216,7 +7537,7 @@
         <v>119</v>
       </c>
       <c r="B33" s="31"/>
-      <c r="C33" s="31">
+      <c r="C33" s="23">
         <v>692</v>
       </c>
       <c r="D33" s="31"/>
@@ -7235,7 +7556,7 @@
         <v>120</v>
       </c>
       <c r="B34" s="31"/>
-      <c r="C34" s="31">
+      <c r="C34" s="23">
         <v>45</v>
       </c>
       <c r="D34" s="31"/>
@@ -7254,7 +7575,7 @@
         <v>121</v>
       </c>
       <c r="B35" s="31"/>
-      <c r="C35" s="31">
+      <c r="C35" s="23">
         <v>28</v>
       </c>
       <c r="D35" s="31"/>
@@ -7271,7 +7592,7 @@
     <row r="36" spans="1:7" ht="13.2">
       <c r="A36" s="34"/>
       <c r="B36" s="35"/>
-      <c r="C36" s="35"/>
+      <c r="C36" s="12"/>
       <c r="D36" s="35"/>
       <c r="E36" s="35"/>
       <c r="F36" s="41"/>
@@ -7280,7 +7601,7 @@
     <row r="37" spans="1:7" ht="13.2">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
+      <c r="C37" s="135"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -8229,7 +8550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFCE5CD"/>
@@ -8240,7 +8561,7 @@
   <cols>
     <col min="1" max="1" width="39.6640625" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" style="163" customWidth="1"/>
     <col min="4" max="7" width="25.109375" customWidth="1"/>
     <col min="8" max="8" width="2.6640625" customWidth="1"/>
     <col min="9" max="27" width="12.6640625" hidden="1"/>
@@ -8276,7 +8597,7 @@
       <c r="B3" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="13" t="s">
         <v>40</v>
       </c>
       <c r="D3" s="21" t="s">
@@ -8297,8 +8618,8 @@
         <v>123</v>
       </c>
       <c r="B4" s="44"/>
-      <c r="C4" s="44">
-        <v>1.09E-2</v>
+      <c r="C4" s="156" t="s">
+        <v>259</v>
       </c>
       <c r="D4" s="45"/>
       <c r="E4" s="45" t="s">
@@ -8316,8 +8637,8 @@
         <v>125</v>
       </c>
       <c r="B5" s="44"/>
-      <c r="C5" s="44">
-        <v>2.4899999999999999E-2</v>
+      <c r="C5" s="156" t="s">
+        <v>260</v>
       </c>
       <c r="D5" s="45"/>
       <c r="E5" s="45" t="s">
@@ -8335,8 +8656,8 @@
         <v>126</v>
       </c>
       <c r="B6" s="44"/>
-      <c r="C6" s="44">
-        <v>0.23899999999999999</v>
+      <c r="C6" s="156" t="s">
+        <v>261</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="47" t="s">
@@ -8354,8 +8675,8 @@
         <v>127</v>
       </c>
       <c r="B7" s="49"/>
-      <c r="C7" s="49">
-        <v>0.22700000000000001</v>
+      <c r="C7" s="157" t="s">
+        <v>262</v>
       </c>
       <c r="D7" s="50"/>
       <c r="E7" s="50" t="s">
@@ -8373,8 +8694,8 @@
         <v>128</v>
       </c>
       <c r="B8" s="49"/>
-      <c r="C8" s="49">
-        <v>7.6300000000000007E-2</v>
+      <c r="C8" s="157" t="s">
+        <v>263</v>
       </c>
       <c r="D8" s="50"/>
       <c r="E8" s="50" t="s">
@@ -8392,8 +8713,8 @@
         <v>129</v>
       </c>
       <c r="B9" s="49"/>
-      <c r="C9" s="49">
-        <v>0.10299999999999999</v>
+      <c r="C9" s="157" t="s">
+        <v>264</v>
       </c>
       <c r="D9" s="50"/>
       <c r="E9" s="50" t="s">
@@ -8411,8 +8732,8 @@
         <v>130</v>
       </c>
       <c r="B10" s="49"/>
-      <c r="C10" s="49">
-        <v>2.1700000000000001E-2</v>
+      <c r="C10" s="157" t="s">
+        <v>265</v>
       </c>
       <c r="D10" s="50"/>
       <c r="E10" s="50" t="s">
@@ -8430,8 +8751,8 @@
         <v>132</v>
       </c>
       <c r="B11" s="49"/>
-      <c r="C11" s="49">
-        <v>0.122</v>
+      <c r="C11" s="157" t="s">
+        <v>266</v>
       </c>
       <c r="D11" s="50"/>
       <c r="E11" s="50" t="s">
@@ -8449,8 +8770,8 @@
         <v>133</v>
       </c>
       <c r="B12" s="44"/>
-      <c r="C12" s="44">
-        <v>0.14599999999999999</v>
+      <c r="C12" s="156" t="s">
+        <v>267</v>
       </c>
       <c r="D12" s="45"/>
       <c r="E12" s="45" t="s">
@@ -8468,8 +8789,8 @@
         <v>134</v>
       </c>
       <c r="B13" s="49"/>
-      <c r="C13" s="49">
-        <v>0.13700000000000001</v>
+      <c r="C13" s="157" t="s">
+        <v>268</v>
       </c>
       <c r="D13" s="50"/>
       <c r="E13" s="50" t="s">
@@ -8487,8 +8808,8 @@
         <v>135</v>
       </c>
       <c r="B14" s="49"/>
-      <c r="C14" s="49">
-        <v>0.129</v>
+      <c r="C14" s="157" t="s">
+        <v>269</v>
       </c>
       <c r="D14" s="50"/>
       <c r="E14" s="50" t="s">
@@ -8506,8 +8827,8 @@
         <v>136</v>
       </c>
       <c r="B15" s="55"/>
-      <c r="C15" s="55">
-        <v>5.7000000000000002E-3</v>
+      <c r="C15" s="158" t="s">
+        <v>270</v>
       </c>
       <c r="D15" s="50"/>
       <c r="E15" s="50" t="s">
@@ -8525,8 +8846,8 @@
         <v>137</v>
       </c>
       <c r="B16" s="55"/>
-      <c r="C16" s="55">
-        <v>5.7000000000000002E-3</v>
+      <c r="C16" s="158" t="s">
+        <v>270</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="50" t="s">
@@ -8544,8 +8865,8 @@
         <v>138</v>
       </c>
       <c r="B17" s="55"/>
-      <c r="C17" s="55">
-        <v>6.0000000000000001E-3</v>
+      <c r="C17" s="158" t="s">
+        <v>271</v>
       </c>
       <c r="D17" s="50"/>
       <c r="E17" s="50" t="s">
@@ -8563,8 +8884,8 @@
         <v>139</v>
       </c>
       <c r="B18" s="57"/>
-      <c r="C18" s="57">
-        <v>3.6900000000000001E-3</v>
+      <c r="C18" s="159" t="s">
+        <v>272</v>
       </c>
       <c r="D18" s="45"/>
       <c r="E18" s="45" t="s">
@@ -8584,7 +8905,7 @@
       <c r="B20" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="13" t="s">
         <v>40</v>
       </c>
       <c r="D20" s="21" t="s">
@@ -8606,8 +8927,8 @@
         <v>123</v>
       </c>
       <c r="B21" s="44"/>
-      <c r="C21" s="44">
-        <v>1.09E-2</v>
+      <c r="C21" s="156" t="s">
+        <v>259</v>
       </c>
       <c r="D21" s="45"/>
       <c r="E21" s="45" t="s">
@@ -8626,8 +8947,8 @@
         <v>125</v>
       </c>
       <c r="B22" s="44"/>
-      <c r="C22" s="44">
-        <v>2.4899999999999999E-2</v>
+      <c r="C22" s="156" t="s">
+        <v>260</v>
       </c>
       <c r="D22" s="45"/>
       <c r="E22" s="45" t="s">
@@ -8646,8 +8967,8 @@
         <v>126</v>
       </c>
       <c r="B23" s="44"/>
-      <c r="C23" s="44">
-        <v>0.23899999999999999</v>
+      <c r="C23" s="156" t="s">
+        <v>261</v>
       </c>
       <c r="D23" s="45"/>
       <c r="E23" s="45" t="s">
@@ -8666,8 +8987,8 @@
         <v>127</v>
       </c>
       <c r="B24" s="49"/>
-      <c r="C24" s="49">
-        <v>0.22700000000000001</v>
+      <c r="C24" s="157" t="s">
+        <v>262</v>
       </c>
       <c r="D24" s="50"/>
       <c r="E24" s="50" t="s">
@@ -8691,8 +9012,8 @@
         <v>128</v>
       </c>
       <c r="B25" s="49"/>
-      <c r="C25" s="49">
-        <v>7.6300000000000007E-2</v>
+      <c r="C25" s="157" t="s">
+        <v>263</v>
       </c>
       <c r="D25" s="50"/>
       <c r="E25" s="50" t="s">
@@ -8714,8 +9035,8 @@
         <v>129</v>
       </c>
       <c r="B26" s="49"/>
-      <c r="C26" s="49">
-        <v>0.10299999999999999</v>
+      <c r="C26" s="157" t="s">
+        <v>264</v>
       </c>
       <c r="D26" s="50"/>
       <c r="E26" s="50" t="s">
@@ -8737,8 +9058,8 @@
         <v>130</v>
       </c>
       <c r="B27" s="49"/>
-      <c r="C27" s="49">
-        <v>2.1700000000000001E-2</v>
+      <c r="C27" s="157" t="s">
+        <v>265</v>
       </c>
       <c r="D27" s="50"/>
       <c r="E27" s="50" t="s">
@@ -8760,8 +9081,8 @@
         <v>132</v>
       </c>
       <c r="B28" s="49"/>
-      <c r="C28" s="49">
-        <v>0.122</v>
+      <c r="C28" s="157" t="s">
+        <v>266</v>
       </c>
       <c r="D28" s="50"/>
       <c r="E28" s="50" t="s">
@@ -8783,8 +9104,8 @@
         <v>133</v>
       </c>
       <c r="B29" s="44"/>
-      <c r="C29" s="44">
-        <v>0.14599999999999999</v>
+      <c r="C29" s="156" t="s">
+        <v>267</v>
       </c>
       <c r="D29" s="45"/>
       <c r="E29" s="45" t="s">
@@ -8806,8 +9127,8 @@
         <v>134</v>
       </c>
       <c r="B30" s="49"/>
-      <c r="C30" s="49">
-        <v>0.13700000000000001</v>
+      <c r="C30" s="157" t="s">
+        <v>268</v>
       </c>
       <c r="D30" s="50"/>
       <c r="E30" s="50" t="s">
@@ -8829,8 +9150,8 @@
         <v>135</v>
       </c>
       <c r="B31" s="49"/>
-      <c r="C31" s="49">
-        <v>0.129</v>
+      <c r="C31" s="157" t="s">
+        <v>269</v>
       </c>
       <c r="D31" s="50"/>
       <c r="E31" s="50" t="s">
@@ -8852,8 +9173,8 @@
         <v>136</v>
       </c>
       <c r="B32" s="55"/>
-      <c r="C32" s="55">
-        <v>5.7000000000000002E-3</v>
+      <c r="C32" s="158" t="s">
+        <v>270</v>
       </c>
       <c r="D32" s="50"/>
       <c r="E32" s="50" t="s">
@@ -8875,8 +9196,8 @@
         <v>137</v>
       </c>
       <c r="B33" s="55"/>
-      <c r="C33" s="55">
-        <v>5.7000000000000002E-3</v>
+      <c r="C33" s="158" t="s">
+        <v>270</v>
       </c>
       <c r="D33" s="50"/>
       <c r="E33" s="50" t="s">
@@ -8898,8 +9219,8 @@
         <v>138</v>
       </c>
       <c r="B34" s="55"/>
-      <c r="C34" s="55">
-        <v>6.0000000000000001E-3</v>
+      <c r="C34" s="158" t="s">
+        <v>271</v>
       </c>
       <c r="D34" s="50"/>
       <c r="E34" s="50" t="s">
@@ -8922,8 +9243,8 @@
         <v>139</v>
       </c>
       <c r="B35" s="57"/>
-      <c r="C35" s="57">
-        <v>3.6900000000000001E-3</v>
+      <c r="C35" s="159" t="s">
+        <v>272</v>
       </c>
       <c r="D35" s="45"/>
       <c r="E35" s="45" t="s">
@@ -8944,7 +9265,7 @@
     <row r="36" spans="1:31" ht="13.2">
       <c r="A36" s="34"/>
       <c r="B36" s="59"/>
-      <c r="C36" s="59"/>
+      <c r="C36" s="160"/>
       <c r="D36" s="35"/>
       <c r="E36" s="35"/>
       <c r="F36" s="41"/>
@@ -8961,7 +9282,7 @@
       <c r="B37" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="13" t="s">
         <v>40</v>
       </c>
       <c r="D37" s="21" t="s">
@@ -8986,8 +9307,8 @@
         <v>123</v>
       </c>
       <c r="B38" s="44"/>
-      <c r="C38" s="44">
-        <v>1.09E-2</v>
+      <c r="C38" s="156" t="s">
+        <v>259</v>
       </c>
       <c r="D38" s="45"/>
       <c r="E38" s="45" t="s">
@@ -9009,8 +9330,8 @@
         <v>125</v>
       </c>
       <c r="B39" s="44"/>
-      <c r="C39" s="44">
-        <v>2.4899999999999999E-2</v>
+      <c r="C39" s="156" t="s">
+        <v>260</v>
       </c>
       <c r="D39" s="45"/>
       <c r="E39" s="45" t="s">
@@ -9032,8 +9353,8 @@
         <v>126</v>
       </c>
       <c r="B40" s="44"/>
-      <c r="C40" s="44">
-        <v>0.23899999999999999</v>
+      <c r="C40" s="156" t="s">
+        <v>261</v>
       </c>
       <c r="D40" s="45"/>
       <c r="E40" s="45" t="s">
@@ -9052,8 +9373,8 @@
         <v>127</v>
       </c>
       <c r="B41" s="49"/>
-      <c r="C41" s="49">
-        <v>0.22700000000000001</v>
+      <c r="C41" s="157" t="s">
+        <v>262</v>
       </c>
       <c r="D41" s="50"/>
       <c r="E41" s="50" t="s">
@@ -9072,8 +9393,8 @@
         <v>128</v>
       </c>
       <c r="B42" s="49"/>
-      <c r="C42" s="49">
-        <v>7.6300000000000007E-2</v>
+      <c r="C42" s="157" t="s">
+        <v>263</v>
       </c>
       <c r="D42" s="50"/>
       <c r="E42" s="50" t="s">
@@ -9092,8 +9413,8 @@
         <v>129</v>
       </c>
       <c r="B43" s="49"/>
-      <c r="C43" s="49">
-        <v>0.10299999999999999</v>
+      <c r="C43" s="157" t="s">
+        <v>264</v>
       </c>
       <c r="D43" s="50"/>
       <c r="E43" s="50" t="s">
@@ -9112,8 +9433,8 @@
         <v>130</v>
       </c>
       <c r="B44" s="49"/>
-      <c r="C44" s="49">
-        <v>2.1700000000000001E-2</v>
+      <c r="C44" s="157" t="s">
+        <v>265</v>
       </c>
       <c r="D44" s="50"/>
       <c r="E44" s="50" t="s">
@@ -9132,8 +9453,8 @@
         <v>132</v>
       </c>
       <c r="B45" s="49"/>
-      <c r="C45" s="49">
-        <v>0.122</v>
+      <c r="C45" s="157" t="s">
+        <v>266</v>
       </c>
       <c r="D45" s="50"/>
       <c r="E45" s="50" t="s">
@@ -9152,8 +9473,8 @@
         <v>133</v>
       </c>
       <c r="B46" s="44"/>
-      <c r="C46" s="44">
-        <v>0.14599999999999999</v>
+      <c r="C46" s="156" t="s">
+        <v>267</v>
       </c>
       <c r="D46" s="45"/>
       <c r="E46" s="45" t="s">
@@ -9172,8 +9493,8 @@
         <v>134</v>
       </c>
       <c r="B47" s="49"/>
-      <c r="C47" s="49">
-        <v>0.13700000000000001</v>
+      <c r="C47" s="157" t="s">
+        <v>268</v>
       </c>
       <c r="D47" s="50"/>
       <c r="E47" s="50" t="s">
@@ -9192,8 +9513,8 @@
         <v>135</v>
       </c>
       <c r="B48" s="49"/>
-      <c r="C48" s="49">
-        <v>0.129</v>
+      <c r="C48" s="157" t="s">
+        <v>269</v>
       </c>
       <c r="D48" s="50"/>
       <c r="E48" s="50" t="s">
@@ -9212,8 +9533,8 @@
         <v>136</v>
       </c>
       <c r="B49" s="55"/>
-      <c r="C49" s="55">
-        <v>5.7000000000000002E-3</v>
+      <c r="C49" s="158" t="s">
+        <v>270</v>
       </c>
       <c r="D49" s="50"/>
       <c r="E49" s="50" t="s">
@@ -9232,8 +9553,8 @@
         <v>137</v>
       </c>
       <c r="B50" s="55"/>
-      <c r="C50" s="55">
-        <v>5.7000000000000002E-3</v>
+      <c r="C50" s="158" t="s">
+        <v>270</v>
       </c>
       <c r="D50" s="50"/>
       <c r="E50" s="50" t="s">
@@ -9252,8 +9573,8 @@
         <v>138</v>
       </c>
       <c r="B51" s="55"/>
-      <c r="C51" s="55">
-        <v>6.0000000000000001E-3</v>
+      <c r="C51" s="158" t="s">
+        <v>271</v>
       </c>
       <c r="D51" s="50"/>
       <c r="E51" s="50" t="s">
@@ -9273,8 +9594,8 @@
         <v>139</v>
       </c>
       <c r="B52" s="57"/>
-      <c r="C52" s="57">
-        <v>3.6900000000000001E-3</v>
+      <c r="C52" s="159" t="s">
+        <v>272</v>
       </c>
       <c r="D52" s="45"/>
       <c r="E52" s="45" t="s">
@@ -9292,7 +9613,7 @@
     <row r="53" spans="1:9" ht="13.2">
       <c r="A53" s="60"/>
       <c r="B53" s="61"/>
-      <c r="C53" s="61"/>
+      <c r="C53" s="161"/>
       <c r="D53" s="62"/>
       <c r="E53" s="62"/>
       <c r="F53" s="63"/>
@@ -9301,7 +9622,7 @@
     <row r="54" spans="1:9" ht="13.2">
       <c r="A54" s="4"/>
       <c r="B54" s="64"/>
-      <c r="C54" s="64"/>
+      <c r="C54" s="162"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
@@ -10275,7 +10596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFCE5CD"/>
@@ -10286,7 +10607,7 @@
   <cols>
     <col min="1" max="1" width="28.88671875" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" style="134" customWidth="1"/>
     <col min="4" max="7" width="25.109375" customWidth="1"/>
     <col min="8" max="8" width="5.88671875" customWidth="1"/>
     <col min="9" max="10" width="25.109375" customWidth="1"/>
@@ -10295,7 +10616,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="22.8">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="121" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="115"/>
@@ -10350,8 +10671,8 @@
         <v>143</v>
       </c>
       <c r="B4" s="67"/>
-      <c r="C4" s="67">
-        <v>0.36699999999999999</v>
+      <c r="C4" s="136" t="s">
+        <v>273</v>
       </c>
       <c r="D4" s="53"/>
       <c r="E4" s="53" t="s">
@@ -10369,8 +10690,8 @@
         <v>145</v>
       </c>
       <c r="B5" s="69"/>
-      <c r="C5" s="69">
-        <v>1.1000000000000001</v>
+      <c r="C5" s="137" t="s">
+        <v>274</v>
       </c>
       <c r="D5" s="53"/>
       <c r="E5" s="53" t="s">
@@ -10388,8 +10709,8 @@
         <v>147</v>
       </c>
       <c r="B6" s="70"/>
-      <c r="C6" s="70">
-        <v>0.91700000000000004</v>
+      <c r="C6" s="138" t="s">
+        <v>275</v>
       </c>
       <c r="D6" s="53"/>
       <c r="E6" s="53" t="s">
@@ -10407,8 +10728,8 @@
         <v>148</v>
       </c>
       <c r="B7" s="71"/>
-      <c r="C7" s="71">
-        <v>2.29</v>
+      <c r="C7" s="139" t="s">
+        <v>276</v>
       </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53" t="s">
@@ -10426,8 +10747,8 @@
         <v>149</v>
       </c>
       <c r="B8" s="72"/>
-      <c r="C8" s="72">
-        <v>6.5299999999999997E-2</v>
+      <c r="C8" s="140" t="s">
+        <v>277</v>
       </c>
       <c r="D8" s="66"/>
       <c r="E8" s="66" t="s">
@@ -10445,8 +10766,8 @@
         <v>150</v>
       </c>
       <c r="B9" s="72"/>
-      <c r="C9" s="72">
-        <v>0.13700000000000001</v>
+      <c r="C9" s="140" t="s">
+        <v>268</v>
       </c>
       <c r="D9" s="66"/>
       <c r="E9" s="66" t="s">
@@ -10462,7 +10783,7 @@
     <row r="10" spans="1:11" ht="13.2">
       <c r="A10" s="73"/>
       <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
+      <c r="C10" s="141"/>
       <c r="D10" s="75"/>
       <c r="E10" s="75"/>
       <c r="F10" s="76"/>
@@ -10496,8 +10817,8 @@
         <v>151</v>
       </c>
       <c r="B12" s="79"/>
-      <c r="C12" s="79">
-        <v>1.44</v>
+      <c r="C12" s="142" t="s">
+        <v>278</v>
       </c>
       <c r="D12" s="80"/>
       <c r="E12" s="80" t="s">
@@ -10517,8 +10838,8 @@
         <v>153</v>
       </c>
       <c r="B13" s="81"/>
-      <c r="C13" s="81">
-        <v>2.2000000000000002</v>
+      <c r="C13" s="143" t="s">
+        <v>279</v>
       </c>
       <c r="D13" s="80"/>
       <c r="E13" s="80" t="s">
@@ -10538,7 +10859,7 @@
         <v>154</v>
       </c>
       <c r="B14" s="82"/>
-      <c r="C14" s="82">
+      <c r="C14" s="144">
         <v>458</v>
       </c>
       <c r="D14" s="66"/>
@@ -10559,8 +10880,8 @@
         <v>155</v>
       </c>
       <c r="B15" s="83"/>
-      <c r="C15" s="83">
-        <v>0.215</v>
+      <c r="C15" s="145" t="s">
+        <v>280</v>
       </c>
       <c r="D15" s="66"/>
       <c r="E15" s="66" t="s">
@@ -10580,8 +10901,8 @@
         <v>156</v>
       </c>
       <c r="B16" s="79"/>
-      <c r="C16" s="79">
-        <v>1.29</v>
+      <c r="C16" s="142" t="s">
+        <v>281</v>
       </c>
       <c r="D16" s="66"/>
       <c r="E16" s="66" t="s">
@@ -10601,8 +10922,8 @@
         <v>157</v>
       </c>
       <c r="B17" s="83"/>
-      <c r="C17" s="83">
-        <v>0.47199999999999998</v>
+      <c r="C17" s="145" t="s">
+        <v>282</v>
       </c>
       <c r="D17" s="66"/>
       <c r="E17" s="66" t="s">
@@ -10622,8 +10943,8 @@
         <v>158</v>
       </c>
       <c r="B18" s="79"/>
-      <c r="C18" s="79">
-        <v>0.22</v>
+      <c r="C18" s="142" t="s">
+        <v>283</v>
       </c>
       <c r="D18" s="66"/>
       <c r="E18" s="66" t="s">
@@ -10643,8 +10964,8 @@
         <v>159</v>
       </c>
       <c r="B19" s="79"/>
-      <c r="C19" s="79">
-        <v>1.47</v>
+      <c r="C19" s="142" t="s">
+        <v>284</v>
       </c>
       <c r="D19" s="66"/>
       <c r="E19" s="66" t="s">
@@ -10664,8 +10985,8 @@
         <v>160</v>
       </c>
       <c r="B20" s="83"/>
-      <c r="C20" s="83">
-        <v>0.53500000000000003</v>
+      <c r="C20" s="145" t="s">
+        <v>285</v>
       </c>
       <c r="D20" s="66"/>
       <c r="E20" s="66" t="s">
@@ -10685,8 +11006,8 @@
         <v>161</v>
       </c>
       <c r="B21" s="83"/>
-      <c r="C21" s="83">
-        <v>0.63700000000000001</v>
+      <c r="C21" s="145" t="s">
+        <v>286</v>
       </c>
       <c r="D21" s="66"/>
       <c r="E21" s="66" t="s">
@@ -10706,8 +11027,8 @@
         <v>162</v>
       </c>
       <c r="B22" s="83"/>
-      <c r="C22" s="83">
-        <v>0.54700000000000004</v>
+      <c r="C22" s="145" t="s">
+        <v>287</v>
       </c>
       <c r="D22" s="66"/>
       <c r="E22" s="66" t="s">
@@ -10727,8 +11048,8 @@
         <v>163</v>
       </c>
       <c r="B23" s="79"/>
-      <c r="C23" s="79">
-        <v>4.18</v>
+      <c r="C23" s="142" t="s">
+        <v>288</v>
       </c>
       <c r="D23" s="66"/>
       <c r="E23" s="66" t="s">
@@ -10748,8 +11069,8 @@
         <v>164</v>
       </c>
       <c r="B24" s="79"/>
-      <c r="C24" s="79">
-        <v>1.23</v>
+      <c r="C24" s="142" t="s">
+        <v>289</v>
       </c>
       <c r="D24" s="66"/>
       <c r="E24" s="66" t="s">
@@ -10769,8 +11090,8 @@
         <v>165</v>
       </c>
       <c r="B25" s="79"/>
-      <c r="C25" s="79">
-        <v>1.18</v>
+      <c r="C25" s="142" t="s">
+        <v>290</v>
       </c>
       <c r="D25" s="66"/>
       <c r="E25" s="66" t="s">
@@ -10788,8 +11109,8 @@
         <v>166</v>
       </c>
       <c r="B26" s="79"/>
-      <c r="C26" s="79">
-        <v>1.31</v>
+      <c r="C26" s="142" t="s">
+        <v>291</v>
       </c>
       <c r="D26" s="66"/>
       <c r="E26" s="66" t="s">
@@ -10807,8 +11128,8 @@
         <v>168</v>
       </c>
       <c r="B27" s="79"/>
-      <c r="C27" s="79">
-        <v>2.29</v>
+      <c r="C27" s="142" t="s">
+        <v>276</v>
       </c>
       <c r="D27" s="66"/>
       <c r="E27" s="66" t="s">
@@ -10824,7 +11145,7 @@
     <row r="28" spans="1:10" ht="13.2">
       <c r="A28" s="77"/>
       <c r="B28" s="84"/>
-      <c r="C28" s="84"/>
+      <c r="C28" s="146"/>
       <c r="D28" s="84"/>
       <c r="E28" s="84"/>
       <c r="F28" s="84"/>
@@ -10858,8 +11179,8 @@
         <v>169</v>
       </c>
       <c r="B30" s="85"/>
-      <c r="C30" s="85">
-        <v>5.5</v>
+      <c r="C30" s="147" t="s">
+        <v>292</v>
       </c>
       <c r="D30" s="66"/>
       <c r="E30" s="66" t="s">
@@ -10877,7 +11198,7 @@
         <v>170</v>
       </c>
       <c r="B31" s="86"/>
-      <c r="C31" s="86">
+      <c r="C31" s="148">
         <v>1</v>
       </c>
       <c r="D31" s="66"/>
@@ -10896,8 +11217,8 @@
         <v>171</v>
       </c>
       <c r="B32" s="85"/>
-      <c r="C32" s="85">
-        <v>0.8</v>
+      <c r="C32" s="147" t="s">
+        <v>293</v>
       </c>
       <c r="D32" s="66"/>
       <c r="E32" s="66" t="s">
@@ -10915,7 +11236,7 @@
         <v>172</v>
       </c>
       <c r="B33" s="86"/>
-      <c r="C33" s="86">
+      <c r="C33" s="148">
         <v>16</v>
       </c>
       <c r="D33" s="66"/>
@@ -10934,7 +11255,7 @@
         <v>173</v>
       </c>
       <c r="B34" s="86"/>
-      <c r="C34" s="86">
+      <c r="C34" s="148">
         <v>62</v>
       </c>
       <c r="D34" s="66"/>
@@ -10953,7 +11274,7 @@
         <v>174</v>
       </c>
       <c r="B35" s="86"/>
-      <c r="C35" s="86">
+      <c r="C35" s="148">
         <v>920</v>
       </c>
       <c r="D35" s="66"/>
@@ -10972,7 +11293,7 @@
         <v>175</v>
       </c>
       <c r="B36" s="86"/>
-      <c r="C36" s="86">
+      <c r="C36" s="148">
         <v>480</v>
       </c>
       <c r="D36" s="66"/>
@@ -10991,8 +11312,8 @@
         <v>176</v>
       </c>
       <c r="B37" s="85"/>
-      <c r="C37" s="85">
-        <v>4.5999999999999996</v>
+      <c r="C37" s="147" t="s">
+        <v>294</v>
       </c>
       <c r="D37" s="66"/>
       <c r="E37" s="66" t="s">
@@ -11010,8 +11331,8 @@
         <v>177</v>
       </c>
       <c r="B38" s="87"/>
-      <c r="C38" s="87">
-        <v>4.12</v>
+      <c r="C38" s="149" t="s">
+        <v>295</v>
       </c>
       <c r="D38" s="66"/>
       <c r="E38" s="66" t="s">
@@ -11029,8 +11350,8 @@
         <v>178</v>
       </c>
       <c r="B39" s="87"/>
-      <c r="C39" s="87">
-        <v>2.25</v>
+      <c r="C39" s="149" t="s">
+        <v>237</v>
       </c>
       <c r="D39" s="66"/>
       <c r="E39" s="66" t="s">
@@ -11048,8 +11369,8 @@
         <v>179</v>
       </c>
       <c r="B40" s="85"/>
-      <c r="C40" s="85">
-        <v>2.5</v>
+      <c r="C40" s="147" t="s">
+        <v>296</v>
       </c>
       <c r="D40" s="66"/>
       <c r="E40" s="66" t="s">
@@ -11065,7 +11386,7 @@
     <row r="41" spans="1:39" ht="13.2">
       <c r="A41" s="77"/>
       <c r="B41" s="84"/>
-      <c r="C41" s="84"/>
+      <c r="C41" s="146"/>
       <c r="D41" s="77"/>
       <c r="E41" s="77"/>
       <c r="F41" s="88"/>
@@ -11109,8 +11430,8 @@
         <v>180</v>
       </c>
       <c r="B43" s="93"/>
-      <c r="C43" s="93">
-        <v>0.92</v>
+      <c r="C43" s="150" t="s">
+        <v>297</v>
       </c>
       <c r="D43" s="94"/>
       <c r="E43" s="94" t="s">
@@ -11160,7 +11481,7 @@
         <v>181</v>
       </c>
       <c r="B44" s="93"/>
-      <c r="C44" s="93">
+      <c r="C44" s="150">
         <v>737</v>
       </c>
       <c r="D44" s="94"/>
@@ -11211,7 +11532,7 @@
         <v>182</v>
       </c>
       <c r="B45" s="93"/>
-      <c r="C45" s="93">
+      <c r="C45" s="150">
         <v>496</v>
       </c>
       <c r="D45" s="94"/>
@@ -11262,7 +11583,7 @@
         <v>183</v>
       </c>
       <c r="B46" s="93"/>
-      <c r="C46" s="93">
+      <c r="C46" s="150">
         <v>437</v>
       </c>
       <c r="D46" s="94"/>
@@ -11313,7 +11634,7 @@
         <v>184</v>
       </c>
       <c r="B47" s="93"/>
-      <c r="C47" s="93">
+      <c r="C47" s="150">
         <v>1490</v>
       </c>
       <c r="D47" s="94"/>
@@ -12330,7 +12651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFCE5CD"/>
@@ -12341,13 +12662,13 @@
   <cols>
     <col min="1" max="1" width="40.88671875" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17" style="134" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="25.109375" customWidth="1"/>
     <col min="9" max="11" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22.8">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="121" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="115"/>
@@ -12417,7 +12738,7 @@
         <v>186</v>
       </c>
       <c r="B5" s="100"/>
-      <c r="C5" s="100">
+      <c r="C5" s="151">
         <v>440</v>
       </c>
       <c r="D5" s="101"/>
@@ -12442,7 +12763,7 @@
         <v>188</v>
       </c>
       <c r="B6" s="100"/>
-      <c r="C6" s="100">
+      <c r="C6" s="151">
         <v>319</v>
       </c>
       <c r="D6" s="101"/>
@@ -12467,7 +12788,7 @@
         <v>189</v>
       </c>
       <c r="B7" s="100"/>
-      <c r="C7" s="100">
+      <c r="C7" s="151">
         <v>73</v>
       </c>
       <c r="D7" s="101"/>
@@ -12492,7 +12813,7 @@
         <v>190</v>
       </c>
       <c r="B8" s="100"/>
-      <c r="C8" s="100">
+      <c r="C8" s="151">
         <v>165</v>
       </c>
       <c r="D8" s="101"/>
@@ -12522,7 +12843,7 @@
         <v>191</v>
       </c>
       <c r="B9" s="100"/>
-      <c r="C9" s="100">
+      <c r="C9" s="151">
         <v>656</v>
       </c>
       <c r="D9" s="101"/>
@@ -12550,7 +12871,7 @@
         <v>192</v>
       </c>
       <c r="B10" s="100"/>
-      <c r="C10" s="100">
+      <c r="C10" s="151">
         <v>220</v>
       </c>
       <c r="D10" s="101"/>
@@ -12578,7 +12899,7 @@
         <v>193</v>
       </c>
       <c r="B11" s="100"/>
-      <c r="C11" s="100">
+      <c r="C11" s="151">
         <v>235</v>
       </c>
       <c r="D11" s="101"/>
@@ -12604,7 +12925,7 @@
     <row r="12" spans="1:14" ht="13.2">
       <c r="A12" s="106"/>
       <c r="B12" s="107"/>
-      <c r="C12" s="107"/>
+      <c r="C12" s="152"/>
       <c r="D12" s="108"/>
       <c r="E12" s="108"/>
       <c r="F12" s="109"/>
@@ -12654,7 +12975,7 @@
         <v>195</v>
       </c>
       <c r="B14" s="86"/>
-      <c r="C14" s="86">
+      <c r="C14" s="148">
         <v>169</v>
       </c>
       <c r="D14" s="66"/>
@@ -12682,7 +13003,7 @@
         <v>196</v>
       </c>
       <c r="B15" s="86"/>
-      <c r="C15" s="86">
+      <c r="C15" s="148">
         <v>156</v>
       </c>
       <c r="D15" s="66"/>
@@ -12710,8 +13031,8 @@
         <v>197</v>
       </c>
       <c r="B16" s="86"/>
-      <c r="C16" s="85">
-        <v>63.2</v>
+      <c r="C16" s="147" t="s">
+        <v>298</v>
       </c>
       <c r="D16" s="66"/>
       <c r="E16" s="66" t="s">
@@ -12738,7 +13059,7 @@
         <v>198</v>
       </c>
       <c r="B17" s="86"/>
-      <c r="C17" s="86">
+      <c r="C17" s="148">
         <v>2935</v>
       </c>
       <c r="D17" s="66"/>
@@ -12766,7 +13087,7 @@
         <v>199</v>
       </c>
       <c r="B18" s="86"/>
-      <c r="C18" s="86">
+      <c r="C18" s="148">
         <v>145</v>
       </c>
       <c r="D18" s="66"/>
@@ -12794,7 +13115,7 @@
         <v>200</v>
       </c>
       <c r="B19" s="86"/>
-      <c r="C19" s="86">
+      <c r="C19" s="148">
         <v>600</v>
       </c>
       <c r="D19" s="66"/>
@@ -12822,7 +13143,7 @@
         <v>201</v>
       </c>
       <c r="B20" s="86"/>
-      <c r="C20" s="86">
+      <c r="C20" s="148">
         <v>371</v>
       </c>
       <c r="D20" s="66"/>
@@ -12850,8 +13171,8 @@
         <v>202</v>
       </c>
       <c r="B21" s="87"/>
-      <c r="C21" s="87">
-        <v>2.78</v>
+      <c r="C21" s="149" t="s">
+        <v>299</v>
       </c>
       <c r="D21" s="66"/>
       <c r="E21" s="66" t="s">
@@ -12876,8 +13197,8 @@
         <v>203</v>
       </c>
       <c r="B22" s="85"/>
-      <c r="C22" s="85">
-        <v>80.7</v>
+      <c r="C22" s="147" t="s">
+        <v>300</v>
       </c>
       <c r="D22" s="66"/>
       <c r="E22" s="66" t="s">
@@ -12902,7 +13223,7 @@
         <v>204</v>
       </c>
       <c r="B23" s="86"/>
-      <c r="C23" s="86">
+      <c r="C23" s="148">
         <v>500</v>
       </c>
       <c r="D23" s="66"/>
@@ -12928,7 +13249,7 @@
         <v>205</v>
       </c>
       <c r="B24" s="86"/>
-      <c r="C24" s="86">
+      <c r="C24" s="148">
         <v>123</v>
       </c>
       <c r="D24" s="66"/>
@@ -12954,8 +13275,8 @@
         <v>206</v>
       </c>
       <c r="B25" s="87"/>
-      <c r="C25" s="87">
-        <v>8.98</v>
+      <c r="C25" s="149" t="s">
+        <v>301</v>
       </c>
       <c r="D25" s="66"/>
       <c r="E25" s="66" t="s">
@@ -12980,8 +13301,8 @@
         <v>207</v>
       </c>
       <c r="B26" s="86"/>
-      <c r="C26" s="86">
-        <v>32.799999999999997</v>
+      <c r="C26" s="148" t="s">
+        <v>302</v>
       </c>
       <c r="D26" s="66"/>
       <c r="E26" s="66" t="s">
@@ -13006,7 +13327,7 @@
         <v>208</v>
       </c>
       <c r="B27" s="86"/>
-      <c r="C27" s="86">
+      <c r="C27" s="148">
         <v>248</v>
       </c>
       <c r="D27" s="66"/>
@@ -13032,8 +13353,8 @@
         <v>209</v>
       </c>
       <c r="B28" s="85"/>
-      <c r="C28" s="85">
-        <v>87.9</v>
+      <c r="C28" s="147" t="s">
+        <v>303</v>
       </c>
       <c r="D28" s="66"/>
       <c r="E28" s="66" t="s">
@@ -13056,7 +13377,7 @@
     <row r="29" spans="1:14" ht="13.2">
       <c r="A29" s="106"/>
       <c r="B29" s="106"/>
-      <c r="C29" s="106"/>
+      <c r="C29" s="153"/>
       <c r="D29" s="106"/>
       <c r="E29" s="106"/>
       <c r="F29" s="106"/>
@@ -13102,8 +13423,8 @@
         <v>210</v>
       </c>
       <c r="B31" s="69"/>
-      <c r="C31" s="69">
-        <v>60.1</v>
+      <c r="C31" s="137" t="s">
+        <v>304</v>
       </c>
       <c r="D31" s="53"/>
       <c r="E31" s="53" t="s">
@@ -13128,7 +13449,7 @@
         <v>211</v>
       </c>
       <c r="B32" s="113"/>
-      <c r="C32" s="113">
+      <c r="C32" s="154">
         <v>907</v>
       </c>
       <c r="D32" s="53"/>
@@ -13154,8 +13475,8 @@
         <v>212</v>
       </c>
       <c r="B33" s="67"/>
-      <c r="C33" s="67">
-        <v>18.600000000000001</v>
+      <c r="C33" s="136" t="s">
+        <v>305</v>
       </c>
       <c r="D33" s="53"/>
       <c r="E33" s="53" t="s">
@@ -13180,8 +13501,8 @@
         <v>213</v>
       </c>
       <c r="B34" s="67"/>
-      <c r="C34" s="67">
-        <v>34.4</v>
+      <c r="C34" s="136" t="s">
+        <v>306</v>
       </c>
       <c r="D34" s="53"/>
       <c r="E34" s="53" t="s">
@@ -13204,7 +13525,7 @@
     <row r="35" spans="1:12" ht="13.2">
       <c r="A35" s="106"/>
       <c r="B35" s="106"/>
-      <c r="C35" s="106"/>
+      <c r="C35" s="153"/>
       <c r="D35" s="106"/>
       <c r="E35" s="106"/>
       <c r="F35" s="106"/>
@@ -13250,7 +13571,7 @@
         <v>214</v>
       </c>
       <c r="B37" s="86"/>
-      <c r="C37" s="86">
+      <c r="C37" s="148">
         <v>209</v>
       </c>
       <c r="D37" s="66"/>
@@ -13276,8 +13597,8 @@
         <v>215</v>
       </c>
       <c r="B38" s="85"/>
-      <c r="C38" s="85">
-        <v>70.099999999999994</v>
+      <c r="C38" s="147" t="s">
+        <v>307</v>
       </c>
       <c r="D38" s="66"/>
       <c r="E38" s="66" t="s">
@@ -13302,8 +13623,8 @@
         <v>216</v>
       </c>
       <c r="B39" s="85"/>
-      <c r="C39" s="85">
-        <v>9.9</v>
+      <c r="C39" s="147" t="s">
+        <v>308</v>
       </c>
       <c r="D39" s="66"/>
       <c r="E39" s="66" t="s">
@@ -13328,8 +13649,8 @@
         <v>217</v>
       </c>
       <c r="B40" s="85"/>
-      <c r="C40" s="85">
-        <v>98.4</v>
+      <c r="C40" s="147" t="s">
+        <v>309</v>
       </c>
       <c r="D40" s="66"/>
       <c r="E40" s="66" t="s">
@@ -13354,7 +13675,7 @@
         <v>218</v>
       </c>
       <c r="B41" s="66"/>
-      <c r="C41" s="66">
+      <c r="C41" s="155">
         <v>83</v>
       </c>
       <c r="D41" s="66"/>
@@ -13380,7 +13701,7 @@
         <v>219</v>
       </c>
       <c r="B42" s="66"/>
-      <c r="C42" s="66">
+      <c r="C42" s="155">
         <v>159</v>
       </c>
       <c r="D42" s="66"/>
@@ -13406,8 +13727,8 @@
         <v>220</v>
       </c>
       <c r="B43" s="66"/>
-      <c r="C43" s="66">
-        <v>31.9</v>
+      <c r="C43" s="155" t="s">
+        <v>310</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66" t="s">
@@ -13432,8 +13753,8 @@
         <v>221</v>
       </c>
       <c r="B44" s="66"/>
-      <c r="C44" s="66">
-        <v>22.5</v>
+      <c r="C44" s="155" t="s">
+        <v>311</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66" t="s">
@@ -13458,7 +13779,7 @@
         <v>222</v>
       </c>
       <c r="B45" s="66"/>
-      <c r="C45" s="66">
+      <c r="C45" s="155">
         <v>961</v>
       </c>
       <c r="D45" s="66"/>
@@ -13484,7 +13805,7 @@
         <v>223</v>
       </c>
       <c r="B46" s="66"/>
-      <c r="C46" s="66">
+      <c r="C46" s="155">
         <v>865</v>
       </c>
       <c r="D46" s="66"/>
@@ -13510,7 +13831,7 @@
         <v>224</v>
       </c>
       <c r="B47" s="66"/>
-      <c r="C47" s="66">
+      <c r="C47" s="155">
         <v>271</v>
       </c>
       <c r="D47" s="66"/>
@@ -13536,7 +13857,7 @@
         <v>225</v>
       </c>
       <c r="B48" s="66"/>
-      <c r="C48" s="66">
+      <c r="C48" s="155">
         <v>342</v>
       </c>
       <c r="D48" s="66"/>
@@ -13562,7 +13883,7 @@
         <v>226</v>
       </c>
       <c r="B49" s="66"/>
-      <c r="C49" s="66">
+      <c r="C49" s="155">
         <v>301</v>
       </c>
       <c r="D49" s="66"/>
@@ -13588,7 +13909,7 @@
         <v>227</v>
       </c>
       <c r="B50" s="66"/>
-      <c r="C50" s="66">
+      <c r="C50" s="155">
         <v>415</v>
       </c>
       <c r="D50" s="66"/>
@@ -13614,7 +13935,7 @@
         <v>228</v>
       </c>
       <c r="B51" s="66"/>
-      <c r="C51" s="66">
+      <c r="C51" s="155">
         <v>300</v>
       </c>
       <c r="D51" s="66"/>
@@ -13640,8 +13961,8 @@
         <v>229</v>
       </c>
       <c r="B52" s="66"/>
-      <c r="C52" s="66">
-        <v>43.4</v>
+      <c r="C52" s="155" t="s">
+        <v>312</v>
       </c>
       <c r="D52" s="66"/>
       <c r="E52" s="66" t="s">
@@ -13662,7 +13983,7 @@
     <row r="53" spans="1:12" ht="13.2">
       <c r="A53" s="77"/>
       <c r="B53" s="84"/>
-      <c r="C53" s="84"/>
+      <c r="C53" s="146"/>
       <c r="D53" s="77"/>
       <c r="E53" s="77"/>
       <c r="F53" s="88"/>
@@ -14653,4 +14974,22 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>